--- a/Data/EC/NIT-9008166741.xlsx
+++ b/Data/EC/NIT-9008166741.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1138787C-38C6-4FF3-842E-07610AF31134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{874CA3D0-930F-4A72-B810-1B93EF9CF7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{4C5F985E-D931-48B3-B322-7E927AB5A827}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EDD09796-CF80-475D-9BD7-7EFAFCC43B0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -728,22 +728,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01A73757-9F5E-38C4-46ED-7B2F24872D7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16420BA3-13C2-FCD4-2D1E-28133B89E1ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -752,7 +752,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -765,7 +765,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1094,23 +1094,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150BAC66-9066-4A0C-BFCA-54E7C3767E59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727C7DD2-4C21-4CFF-82B4-548DB84A667F}">
   <dimension ref="B2:J160"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.86328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1123,7 +1123,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1134,7 +1134,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1145,7 +1145,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1156,8 +1156,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>98</v>
       </c>
@@ -1172,8 +1172,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1188,8 +1188,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>99</v>
       </c>
@@ -1204,8 +1204,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>100</v>
       </c>
@@ -1224,7 +1224,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1276,7 +1276,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1322,7 +1322,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1345,7 +1345,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1368,7 +1368,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1391,7 +1391,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1414,7 +1414,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1437,7 +1437,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1460,7 +1460,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1483,7 +1483,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1552,7 +1552,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1598,7 +1598,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1621,7 +1621,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1644,7 +1644,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1690,7 +1690,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1713,7 +1713,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1736,7 +1736,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1759,7 +1759,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1782,7 +1782,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1805,7 +1805,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1828,7 +1828,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1851,7 +1851,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1874,7 +1874,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1897,7 +1897,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1920,7 +1920,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1943,7 +1943,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1966,7 +1966,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +1989,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2012,7 +2012,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2058,7 +2058,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2081,7 +2081,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2104,7 +2104,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2127,7 +2127,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2150,7 +2150,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2173,7 +2173,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2196,7 +2196,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2219,7 +2219,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2242,7 +2242,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2265,7 +2265,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2288,7 +2288,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2311,7 +2311,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2334,7 +2334,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2357,7 +2357,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2380,7 +2380,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2403,7 +2403,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2426,7 +2426,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2449,7 +2449,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2495,7 +2495,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2518,7 +2518,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2541,7 +2541,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2564,7 +2564,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2587,7 +2587,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2610,7 +2610,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2633,7 +2633,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2656,7 +2656,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2679,7 +2679,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2702,7 +2702,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2725,7 +2725,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2748,7 +2748,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2771,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2794,7 +2794,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2817,7 +2817,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2840,7 +2840,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2863,7 +2863,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2886,7 +2886,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2909,7 +2909,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2932,7 +2932,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2955,7 +2955,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2978,7 +2978,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3001,7 +3001,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3024,7 +3024,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3047,7 +3047,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3070,7 +3070,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3093,7 +3093,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3116,7 +3116,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3139,7 +3139,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3162,7 +3162,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3185,7 +3185,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3208,7 +3208,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3231,7 +3231,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3254,7 +3254,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3277,7 +3277,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3300,7 +3300,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3323,7 +3323,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3346,7 +3346,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3369,7 +3369,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3392,7 +3392,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3415,7 +3415,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3438,7 +3438,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3461,7 +3461,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3484,7 +3484,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3507,7 +3507,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3530,7 +3530,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3553,7 +3553,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3576,7 +3576,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3599,7 +3599,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3622,7 +3622,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3645,7 +3645,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3668,7 +3668,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3691,7 +3691,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3714,7 +3714,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3737,7 +3737,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3760,7 +3760,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3783,7 +3783,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3806,7 +3806,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3829,7 +3829,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3852,7 +3852,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3875,7 +3875,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3898,7 +3898,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3921,7 +3921,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3944,7 +3944,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3967,7 +3967,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3990,7 +3990,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -4013,7 +4013,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -4036,7 +4036,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -4059,7 +4059,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4082,7 +4082,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4105,7 +4105,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4128,7 +4128,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4151,7 +4151,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4174,7 +4174,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4197,7 +4197,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4220,7 +4220,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4243,7 +4243,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4266,7 +4266,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4289,7 +4289,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4312,7 +4312,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4335,7 +4335,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4358,7 +4358,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4381,7 +4381,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4404,7 +4404,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4427,7 +4427,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="21" t="s">
         <v>8</v>
       </c>
@@ -4450,7 +4450,7 @@
       <c r="I154" s="25"/>
       <c r="J154" s="26"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="32" t="s">
         <v>106</v>
       </c>
@@ -4461,7 +4461,7 @@
       <c r="I159" s="1"/>
       <c r="J159" s="1"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="32" t="s">
         <v>105</v>
       </c>
